--- a/notebook_model_inventory.xlsx
+++ b/notebook_model_inventory.xlsx
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_exp/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_linear/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_quadratic/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_5000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_const/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_exp/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_quadratic/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_16/binnGsize_16/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_2/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_8/binnGsize_8/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_11/dataX2num_11/dataTnum_9/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_1/dataNoisePercent_5/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_121/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_2/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_3/binnDGHiddenLayers_4/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_2/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnSurfaceHiddenLayers_4/binnDGHiddenLayers_3/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_100.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/surface_weight_1.0/pde_weight_2.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_1000000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_10000.0/D_bound_(0, 0.1)/D_mono_weight_10000.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_10/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_linear/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_4/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, True, True)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/G_bound_weight_0/G_bound_(-0.48000000000000004, 2.4000000000000004)/G_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnActivation_sigmoid/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/perfectPDE_False/binnActivation_tanh/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_GLS/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_1/dataNoisePercent_1/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_100/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_500/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_1000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_3000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_1/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_4/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_0/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_1/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_128/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_16/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_32/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_64/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>/Users/willa954/Desktop/Git-personal/Hyperparam/hyperparam-selection/Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
+          <t>Training/binn/dataX1num_38/dataX2num_1/dataTnum_5/dataK_1/dataICLabel_cos/dataDiffLabel_const/dataGrowLabel_zero/dataGamma_0/dataNoisePercent_0/dataNoiseSeed_0/binnVF_0.2/binnGenerateIndicesLabel_random/binnTVsplitSeed_2/binnUsize_8/binnDsize_2/binnGsize_None/DoneParamBool_False/binnDevice_cpu/allConstraints_True/constraintTuple_(True, True, False, False)/D_bound_weight_0/D_bound_(0, 0.1)/D_mono_weight_10.0/BNdataLossFuncLabel_MSE/BCbool_0/numPDEsamples_1000/binnLR_0.001/binnBatchSize_38/binnRelUpdateThresh_0.05/binnRelSaveThresh_0.05/binnES_2000/binnModelLabel_0/binnModel0.pth</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
